--- a/data/Negociado_de_Policia/npprDesp.xlsx
+++ b/data/Negociado_de_Policia/npprDesp.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gnper\Documents\ViolenciaGeneroPR\data\Negociado_de_Policia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D96277E3-7E17-4058-AA31-5FAE2D6A573E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8E7D32F-F749-4402-A5C0-37D9DF81737F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -324,13 +324,13 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:K7"/>
   <sheetFormatPr defaultColWidth="12.5546875" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>6</v>
       </c>
@@ -361,8 +361,11 @@
       <c r="J1" s="1">
         <v>2025</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -391,10 +394,13 @@
         <v>197</v>
       </c>
       <c r="J2" s="3">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>152</v>
+      </c>
+      <c r="K2">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
@@ -423,10 +429,13 @@
         <v>191</v>
       </c>
       <c r="J3" s="3">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>142</v>
+      </c>
+      <c r="K3">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
@@ -455,10 +464,13 @@
         <v>6</v>
       </c>
       <c r="J4" s="3">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>10</v>
+      </c>
+      <c r="K4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>3</v>
       </c>
@@ -487,10 +499,13 @@
         <v>132</v>
       </c>
       <c r="J5" s="3">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>110</v>
+      </c>
+      <c r="K5">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>4</v>
       </c>
@@ -519,10 +534,13 @@
         <v>127</v>
       </c>
       <c r="J6" s="3">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>106</v>
+      </c>
+      <c r="K6">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>5</v>
       </c>
@@ -551,7 +569,10 @@
         <v>5</v>
       </c>
       <c r="J7" s="3">
-        <v>7</v>
+        <v>4</v>
+      </c>
+      <c r="K7">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
